--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIAN BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIAN BELGRADE.xlsx
@@ -671,13 +671,13 @@
         <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -752,13 +752,13 @@
         <v>1.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AN2" t="n">
         <v>2.222222222222222</v>
@@ -801,13 +801,13 @@
         <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
@@ -882,13 +882,13 @@
         <v>1.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AN3" t="n">
         <v>2.222222222222222</v>
@@ -931,13 +931,13 @@
         <v>0.2063492063492063</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -1012,13 +1012,13 @@
         <v>1.03448275862069</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AN4" t="n">
         <v>2.285714285714286</v>
@@ -1061,13 +1061,13 @@
         <v>0.2063492063492063</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -1142,13 +1142,13 @@
         <v>1.03448275862069</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AN5" t="n">
         <v>2.285714285714286</v>
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
@@ -1651,16 +1651,16 @@
         <v>22</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         <v>10</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2809,13 +2809,13 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>7</v>
@@ -3136,16 +3136,16 @@
         <v>15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
         <v>4</v>
@@ -3631,16 +3631,16 @@
         <v>114</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
         <v>23</v>
@@ -3796,16 +3796,16 @@
         <v>91</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="n">
         <v>25</v>
@@ -4026,10 +4026,10 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
         <v>2</v>
@@ -4185,16 +4185,16 @@
         <v>22</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4845,10 +4845,10 @@
         <v>10</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5343,13 +5343,13 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
         <v>7</v>
@@ -5670,16 +5670,16 @@
         <v>15</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y34" t="n">
         <v>4</v>
@@ -6165,16 +6165,16 @@
         <v>114</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
         <v>23</v>
@@ -6330,16 +6330,16 @@
         <v>91</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y38" t="n">
         <v>25</v>
